--- a/光伏配储项目/电价数据/2026/圣堂站.xlsx
+++ b/光伏配储项目/电价数据/2026/圣堂站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.50995</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38049</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.5319700000000001</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.54367</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.30479</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.31514</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.30573</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.43858</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.45539</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.44024</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.42366</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.42008</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.40927</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.39932</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.40125</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.38606</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.40254</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.42415</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.41366</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.35574</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.3926</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.3855</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.41805</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.39205</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.42104</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.41501</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.425</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.4135</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.44508</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.35926</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.29983</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.33299</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.25232</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.29472</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.28263</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>-0.01415</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.11363</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>-0.03143</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>-0.02355</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.03684</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.08298999999999999</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>0.006030000000000001</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.14463</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.21178</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.23927</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.15081</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>-0.01344</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.11909</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>-0.01325</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.09284000000000001</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.25243</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>0.07657</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.18426</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.42856</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.1788</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.44476</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.07106999999999999</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>0.24402</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>0.5621699999999999</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>0.6058300000000001</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>0.22219</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.28526</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.29139</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.38004</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>0.29147</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.32544</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.41528</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.35359</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.32729</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.47876</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.4003</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.41179</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.42089</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32999</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.43861</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.15178</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.6922999999999999</v>
+      </c>
+      <c r="F118" t="n">
+        <v>0.30588</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.7945599999999999</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.53659</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.52298</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.50637</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.4645</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.50005</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.37362</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.47382</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.35521</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.38099</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.39216</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.3377</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.37169</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.35728</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.36065</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.37662</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.37658</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.36059</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.3815</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.42256</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.5137699999999999</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.62386</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.72517</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.43609</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.32181</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.31885</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.3462</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.32341</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.12904</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.28954</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.30244</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.16511</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.12271</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.25713</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.19428</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.14764</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.30865</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.12477</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.29536</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.1619</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>-0.00245</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.05839</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.11679</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0.27475</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>0.14171</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>0.34069</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.25519</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.30396</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.20955</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.27572</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.29556</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>-0.0037</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>-0.04366</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.03067</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>-0.01492</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.22983</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>0.25125</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>0.35952</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>0.35635</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>0.27982</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>0.25714</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>0.68153</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.7837000000000001</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>0.76912</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0.7895399999999999</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.30573</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>0.47598</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.13499</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.44139</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.60172</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.4402799999999999</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.43436</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.4035</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.33771</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.37664</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35356</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33313</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32157</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.5164299999999999</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.37166</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.48578</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.37966</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.38124</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.4025</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.39361</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.39103</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.38254</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.36186</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.4343</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.45074</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.33604</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.37174</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.39327</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.36481</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.37068</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35231</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.35763</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.34744</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.36177</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.35517</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.37862</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.39645</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.47426</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.45011</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.44456</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.34907</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.39713</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.35286</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.36886</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.34682</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.21088</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.28951</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.29513</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.30838</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>-0.01459</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.2628</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.24897</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.30554</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.30863</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.29669</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.28189</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.33635</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.27318</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.25778</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>0.13612</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.09109</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.22945</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0.27606</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.01617</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.16881</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.2913</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.3356</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.29817</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.27808</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.20125</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.15533</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.00232</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.08458</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.05454999999999999</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.19637</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.27008</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.31354</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.18465</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>0.26223</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.28188</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>-0.00704</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.07615999999999999</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.20532</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.22616</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.21224</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.05416</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.14096</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.08973</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.09972</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.24053</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.22309</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.27611</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.34952</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34321</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.09589</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.2485</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.32265</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.28783</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.24865</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.34579</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.33467</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.32842</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.33372</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.30419</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.30472</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.46905</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.31522</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.31935</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.30472</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.31909</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.31928</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.29739</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.29999</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.29649</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.29425</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.29695</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.3372</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.33924</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.35944</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.34387</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.39059</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.32166</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.32979</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.31161</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.29934</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.34117</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.24781</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.28246</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.26545</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.05312</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.00523</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>-0.03616</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>-0.009529999999999999</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.27329</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.23469</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.27954</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.2780899999999999</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.30232</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.38051</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>-0.04772</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.07711</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.16693</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.12434</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.00432</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.35813</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.32207</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.03968</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.02436</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.27791</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.02861</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.09053</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>-0.02298</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.02278</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.16245</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.27952</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.28075</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.27899</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.03125</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.16967</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.30618</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>-0.00666</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.29498</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.30321</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.31036</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.29654</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.29586</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.29362</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.28423</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.36653</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.35666</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.33945</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.30048</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.31092</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.31031</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.30653</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.30412</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.28705</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.30558</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.30456</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.28667</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.29063</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.28966</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.28959</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.28947</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.29774</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.29172</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.2948</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.3124</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.30495</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31655</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32447</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32436</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.33283</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32616</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.27824</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.25893</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.02512</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.03674</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.04051</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.04434</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.03951</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.03951</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>-0.01885</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>-0.04436</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>-0.04991</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>-0.04796</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>-0.04939</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.14851</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>-0.00022</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.28737</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.05205</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.14752</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.18638</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.27229</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.17701</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.21062</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.11653</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.27676</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.21813</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.28368</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.37945</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.30262</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.30541</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.30401</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.39949</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.39849</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.40979</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.4675299999999999</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.35383</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.39643</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.40001</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.41349</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35809</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34467</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.3553</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.34895</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.368</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.24983</v>
+      </c>
+      <c r="D122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="E122" t="n">
+        <v>-0.01178</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.28651</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.30844</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.3307</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.31536</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.32989</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.30968</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.2818</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.31068</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.32945</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.34482</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.33232</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.331</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.33093</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.31463</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.32231</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.33651</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.3104</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.29953</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.31041</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.33531</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.33879</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.35002</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.35201</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.34243</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.31601</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>-0.04929</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.0466</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04572</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04577000000000001</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04572</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04505</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04321</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>-0.04218</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>-0.04458</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.10116</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>-0.00262</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>-0.04365</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>-0.04571</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04297</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.0486</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.04849000000000001</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04488</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04343</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04233</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04828</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04858</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>-0.04243</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.04993</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04818</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04478</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04897</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04349</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.07141</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.17768</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.23667</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.25449</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.25486</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.2471</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.28781</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.14458</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.21633</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.1929</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.21184</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.22208</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.19576</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.21707</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.19661</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.24306</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.23628</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.25851</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.29532</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.28173</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.31038</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.3394</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.34548</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.36746</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.36595</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.33053</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.33124</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.3187</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.30566</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.40549</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.331</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.32158</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.30193</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31133</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.27861</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.2585</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.10266</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29156</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.24688</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.25976</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.24576</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27146</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.2815299999999999</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.081</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.05946</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17177</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.14839</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.16012</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15935</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23739</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.21477</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.17554</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.11994</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28643</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.27631</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.32026</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.29141</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.25839</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.25564</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.25502</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>-0.04501</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28118</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32352</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.29732</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.28081</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.25667</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>-0.0133</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.12086</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.07368999999999999</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>-0.00166</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.30576</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.36097</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.15069</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.10893</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>-0.0008</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.05364</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.10844</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.29645</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.17787</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.27385</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.31169</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>-0.04882</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32104</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.16724</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.07834999999999999</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.20534</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47798</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.3264</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.7397699999999999</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.49016</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78532</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.23559</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.29791</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.5761000000000001</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.5216799999999999</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.20848</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.49027</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>0.93589</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>-0.0117</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.4907</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.32253</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>0.69121</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.47578</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>0.98227</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>0.7010599999999999</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.33889</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.79006</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.5303300000000001</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.7873300000000001</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.77679</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.87854</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.87337</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.49226</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.41176</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.39915</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.44914</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.20628</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87936</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.5513400000000001</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.63895</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.53831</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.4986</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45898</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42744</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.44128</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.4512</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.39347</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45399</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.42112</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.35486</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.40083</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.36621</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.37603</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.41493</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.43394</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.34401</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.39182</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.33187</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.35457</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.34933</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.32884</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.39567</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.32894</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.45182</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.35682</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.33093</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.40085</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.5870599999999999</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.42765</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.59622</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.4525</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.6552</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.33255</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>0.82614</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>-0.00463</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>-0.0459</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.8324199999999999</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.41588</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.32545</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>-0.04878</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>-0.04911</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>-0.04913</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.10012</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.30991</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.07576000000000001</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.10154</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.07278</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.09393000000000001</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.06517000000000001</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.08315</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.0645</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.14005</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.07304000000000001</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.05159</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.06612</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>-0.02389</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.06865</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.07812000000000001</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.12927</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.12321</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.13514</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.11859</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.22422</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.28852</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.34432</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.41385</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.45345</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.4162</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.39281</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.37632</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.35432</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32925</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.9549299999999999</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.36056</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.46757</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.40773</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.41986</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.47735</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.38357</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.41092</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.36612</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.33154</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.3538</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.34841</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.29001</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.33068</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.35925</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.34578</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.32305</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.4009</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.50004</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.35719</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.38767</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.34356</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.35091</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.35529</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.37062</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.35772</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.36285</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.31632</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.31347</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.33246</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.33801</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.30125</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.06243</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.2284</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>-0.04987</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.26006</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.29897</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>-0.04468</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.09754</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.27208</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.25168</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.10278</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.28908</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.30798</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.25426</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.35001</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.32192</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.27213</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.29632</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.19355</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.29769</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.32727</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.31984</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.3095</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.34018</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.31789</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.38901</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.37926</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.4325</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.34898</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.28264</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.4232</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.34985</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.44783</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.31937</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.42042</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.35896</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.4017</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.40043</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.5967</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.35003</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.8854500000000001</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.33357</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.13571</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.70345</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.79516</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.6496799999999999</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.58348</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.45041</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.45034</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.50049</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.4399</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.43745</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.41503</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.42351</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.50052</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.43408</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.41291</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.43413</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.39041</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.42801</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.45039</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.3963</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.42349</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.4341</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.41291</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.40025</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.42352</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.39661</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.40248</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.37532</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.30913</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.01215</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>-0.04893</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>0.23767</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.17745</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>-0.04272</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>0.22428</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.23466</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>0.19374</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.04312</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>-0.04945</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>-0.00512</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>-0.0486</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>-0.006480000000000001</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>-0.04902</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>-0.02712</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>-0.04122</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.13581</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.0573</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.28939</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.03318</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.19701</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.38577</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.36801</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.33297</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.34018</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.3293</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.32475</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.31895</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.42452</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.34076</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.34555</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.33987</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.33594</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.32618</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.32943</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.32615</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.32494</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.32414</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.3101</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.32747</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.32618</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.31999</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.31606</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.32018</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.32015</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.3103</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.32516</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.3112799999999999</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.31923</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.32053</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.39238</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.32498</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.3499</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.39994</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.37494</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.3499</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.33878</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.35558</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.33215</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.33454</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.31898</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.27313</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.33423</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.3371</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.30144</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.32067</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>0.05819</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.30956</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.25087</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.14971</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.14878</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.31562</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.15359</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>0.57355</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>0.6061599999999999</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.1445</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.14481</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.14199</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.14885</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.27148</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.14986</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.27801</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.28061</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.14704</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.13184</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.11805</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.11859</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.17509</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.14578</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.15376</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.30583</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.33451</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.34183</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.33393</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.35262</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.31746</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.36955</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.36203</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.40644</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.34362</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.37991</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.34659</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.40029</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.36069</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.38488</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.45043</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.40068</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.39357</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.40184</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.39768</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.4408</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.43987</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.43923</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.44416</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.44425</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.40353</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.39145</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.3986</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.39158</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.35971</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.36035</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.34801</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.34931</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.33967</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.54243</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.38954</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.46864</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.42382</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.4159</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.37012</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.38105</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.38017</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.39366</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.38146</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.37117</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.38149</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.36136</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.39235</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.37121</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.38135</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.35026</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.34798</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.35525</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.34488</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.34067</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.34594</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.34067</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.3460299999999999</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.35651</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.37146</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.38127</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.36095</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.34107</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.34117</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.34033</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.3293</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.34357</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.35145</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.37504</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.28852</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.31282</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.31245</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.30621</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.28524</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>-0.0411</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>-0.03472</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.23462</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.30236</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.24408</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.23526</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.26254</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.29741</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.28122</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31256</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.28494</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.25469</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.30227</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.27205</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.2282</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.28817</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.2886</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.29481</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.27343</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.30883</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.3201</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.32871</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.3107200000000001</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.2893</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.25372</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.26893</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.30152</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.34502</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.3442</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.35671</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.34494</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.31384</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.29946</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.32644</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.18639</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.34161</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.3778</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.35023</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.35445</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.35318</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.41958</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.38982</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.33943</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.36493</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.36838</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.35824</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.38028</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.38035</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.3853</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.34998</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.36024</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.3402</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.36615</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.41894</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.37072</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.38995</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.38059</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.35282</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.34956</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.36031</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.35181</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.34204</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.34783</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.34584</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.35007</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.34722</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.35008</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.34093</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.34264</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.34341</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.33889</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.33857</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.33994</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.3307</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.3412</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.33219</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.35069</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.3441</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.36095</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.31251</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.32626</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.33926</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.32479</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.31265</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.32591</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.31465</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>0.3141600000000001</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.34795</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.32499</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.27787</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.36559</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.39845</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.29295</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.38195</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.26403</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.25688</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.32382</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>-0.04711</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.24177</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.24915</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.19213</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.07214</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.17202</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.24196</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.28016</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.30734</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.2568</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.23964</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.27392</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.28736</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.28229</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.25879</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.28337</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.32243</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.31576</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.30756</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.39875</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.31851</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.31405</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.32195</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.33028</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.29135</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.36461</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.30316</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.30685</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.30793</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.31656</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.30997</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.47235</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.39014</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.71049</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.34021</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.38622</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.33876</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.32518</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.33432</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.35959</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.33225</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.40961</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.26614</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.33755</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.34183</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.3411</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.31421</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.30967</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.3144</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.29746</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.33475</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.30493</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.34733</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.32502</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.32812</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.3255</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.33004</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.32446</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.32499</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.32324</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.32367</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.32624</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.32477</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.32762</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.32897</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.32749</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.32754</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.32405</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.33108</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.32619</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.32096</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.31981</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.32307</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.32643</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.33113</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.33525</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.34607</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.34082</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.34082</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.33524</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.33881</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.32112</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.32081</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.3343</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.34609</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.35057</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.33423</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.32411</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.31471</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.31509</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.32184</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.3142</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.33745</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.27968</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.34155</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.34087</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.29105</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.32441</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.28068</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.32464</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.31829</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.3196</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.32545</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.32852</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.33328</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.33085</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.30339</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.32654</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.3194</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.3198</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.31986</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.31292</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.34829</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.2992</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.27758</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.30836</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.34072</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.32096</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.34013</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.33122</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.35006</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.35008</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.35009</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.35911</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.32543</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.32798</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.34616</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.37549</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.36793</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.36198</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.36831</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.36288</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.37359</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.36221</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.39365</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.38558</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.37164</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.40323</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.35501</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.38008</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.36995</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.36103</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.35033</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.35005</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.34947</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.34923</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.33964</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.35145</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.35593</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.35587</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.35144</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.35085</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.35005</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.34954</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.34947</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.34631</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.36007</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.34711</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.34987</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.34956</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.33706</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.33965</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.34005</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.33969</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.36943</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.32439</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.33839</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.33964</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.34957</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.33674</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.33971</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.34505</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.33595</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.34956</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.34956</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.33639</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.34013</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.32814</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.34862</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.33937</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.33149</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.33554</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.28295</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.32609</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.32752</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.32888</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.3253</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.31832</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.32692</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.31751</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.31795</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.32474</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.32813</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.31885</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.37045</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.32394</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.31923</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.31475</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.31522</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.32217</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.31144</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.32608</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.32074</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.32206</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.32888</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.32986</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.33176</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.336</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.34564</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.35788</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.5757599999999999</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.39115</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.35465</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.35459</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.36574</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.35045</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.35981</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.34723</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.36038</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.36031</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.36235</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.35029</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.37659</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.37965</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.3808</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.3835</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.42964</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.40896</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.38602</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.38553</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.65135</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.83343</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.47288</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.40744</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.45936</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.39337</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.35073</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.35094</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.35965</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.33992</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.34483</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.31392</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.41156</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.37665</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.37175</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.36396</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.36006</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.35983</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.36288</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.3593</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.36098</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.3598</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.35363</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.36067</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.36085</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.35686</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.35238</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.35981</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.36015</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.35981</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.34078</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.3709</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.3588</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.35651</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.36009</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.36009</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.37955</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.36588</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.3799</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.35654</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.3565</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.35114</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.35183</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.35822</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.34979</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.32991</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.31972</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.33149</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.32162</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.26057</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.13318</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.29053</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.28397</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.28258</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.19504</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.24538</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.27856</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>-0.04818</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.27935</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.12514</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.2834100000000001</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.22546</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.28659</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.23689</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.3032</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.30143</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.14315</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.2957</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.19632</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.20583</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.27671</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.27968</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.29465</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.2882</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.30271</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.28279</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.3103399999999999</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.31309</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.3322</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.33134</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.2947</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.33285</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.40491</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.35535</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.39449</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.63737</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.6033200000000001</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.59427</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.45685</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0.62399</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.45569</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>0.36664</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.43034</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.45201</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.39777</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.37302</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.35351</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.47779</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.43068</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.41969</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.37911</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.37507</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.36732</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.36017</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.34551</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.49012</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.39886</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.42327</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.43052</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.41955</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.3994</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.40583</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.41283</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.41046</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.41857</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.4009</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.39719</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.41295</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.41067</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.39448</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.38844</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.4192</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.38854</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.4172</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.39056</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.40038</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.40033</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.41308</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.40012</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.45074</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.44951</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.56086</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.5007699999999999</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.45091</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.31682</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.40971</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.20766</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.30258</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.38043</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.35499</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0.43968</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.18434</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>0.00045</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.005019999999999999</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.30283</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.30189</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.31458</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.35659</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.34596</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.36045</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.26097</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.21065</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.2741</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.08921999999999999</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>-0.04189</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.25655</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0.26819</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>0.71166</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.38702</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.23716</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.09620000000000001</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.04401</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.21373</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.32524</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.31815</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.30067</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.31334</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.33277</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.30911</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.31136</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.30353</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.31812</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.29469</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.29953</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.30775</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.37562</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.48129</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.42384</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.50562</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.5069</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.36333</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.52098</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>0.61229</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>0.40155</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.53495</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0.7148300000000001</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.46513</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.53195</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0.8088500000000001</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.74437</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.59554</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.64397</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.35482</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.39017</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.48044</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.47946</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.4728</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.41944</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.5022</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.41298</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.44514</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.4584</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.43693</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.42654</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.44839</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.41787</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.40085</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.4577</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.39938</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.4071</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.39875</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.38864</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.38003</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.37498</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.36009</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.35689</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.36587</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.37693</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.37129</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.36023</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.35987</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.36587</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.38666</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.39026</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.37964</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.36653</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.36141</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.35514</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.37967</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.39933</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.3602</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.38766</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.38319</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.39369</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.38663</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.35165</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.3683</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.34262</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.32685</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.22827</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.2445</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.15903</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.29948</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.20606</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>0.4146</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>0.05806</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.24567</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.3984</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.41858</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.46958</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.46506</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.49612</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.47577</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.31597</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.31018</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>0.01001</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.18971</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.3026</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.29282</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.31816</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.35266</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.35011</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.34829</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.34869</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.35665</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.35842</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.3450299999999999</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.4092</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.40907</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.36327</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.41177</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.39726</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.38119</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.35768</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.37808</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.38547</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.40584</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.40109</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.34399</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.3651</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.37807</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.39946</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.36009</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.37952</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.35509</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.39963</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.38059</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.37502</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.36036</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.39378</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.37898</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.36408</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.33128</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.44253</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.35422</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.31805</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.31889</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.33263</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.37691</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.35081</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.37676</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.36494</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.3558</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.35364</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.35147</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.35714</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.34766</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.35044</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.34846</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.33924</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.33154</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.33972</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.34043</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.33553</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.34054</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.34554</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.33101</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.33055</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.33801</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.33809</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.3444</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.32574</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.3166600000000001</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.31108</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.32454</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.1276</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.32676</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.32143</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.31573</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.23149</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.2934</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.23308</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.2269</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.2461</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>-0.02458</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.1297</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.22447</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.28509</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>-0.02391</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.14892</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.04338</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.25514</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>-0.03669</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.14232</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.15134</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.00475</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.30318</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.21573</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.2265</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.13884</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.21061</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.26493</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.283</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.25802</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.29638</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.32582</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.28519</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.34915</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.34627</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.34963</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.33445</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.33817</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.3261</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.33069</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.3186</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.314</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.34314</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.30631</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.33707</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.34522</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.31894</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.34306</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.32351</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.34485</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.31928</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.34437</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.34208</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.34237</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.34319</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.36605</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.37076</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.3607</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.35041</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.35052</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.35013</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.35044</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.35194</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.32314</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.32322</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.33882</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.34289</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.31963</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.33989</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.33202</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.32566</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.32057</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.32026</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.31081</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.31051</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.31534</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.31074</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.31127</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.3112</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.31102</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.31717</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.30705</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.30705</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.30954</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.31032</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.30639</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.30705</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.30765</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.31067</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.31161</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.29107</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.22786</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.21734</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.15135</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.18084</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.01483</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>-0.00288</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>-0.04347</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>-0.04451</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>-0.03373</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.04284</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.04966</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.17037</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.21523</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.26719</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.24285</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.24524</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.245</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.25057</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.26405</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.28721</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.2727</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.26922</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.25833</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.30361</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.27761</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.28206</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.26614</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.28143</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.26831</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.28439</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.27435</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.29501</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.36384</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.30179</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.30603</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.28604</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.25705</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.26727</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.25265</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.23722</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.19155</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.05799</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.2979</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.41679</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.03656</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.06748999999999999</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.25102</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.22785</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.2254</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.14957</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.27003</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.26379</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.24632</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.22357</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.20714</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.1906</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.2154</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.22612</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.17082</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.19082</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.22302</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.22294</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.24421</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.23256</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.21571</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.26397</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.22738</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.27029</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.32642</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.27165</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.2473</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.24841</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.18473</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.06711</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>0.49848</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.5025500000000001</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.50919</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.34887</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.02898</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.18762</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.19733</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.09892000000000001</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.04455</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.04985</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>-0.00514</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.20795</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.03255</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.29143</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>-0.04854</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>-0.04627000000000001</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.02799</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.132</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>-0.03928</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.0434</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.00156</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.07587000000000001</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.0274</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>-0.01803</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>0.02454</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.05323</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.19522</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.25627</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.21064</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.2334</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.2614</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.26593</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.2629</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.29072</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.30433</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.2673</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.29165</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.28377</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>0.26356</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>0.29331</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>0.26979</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.3042</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>0.30488</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0.29383</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0.29712</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0.29734</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>0.3424700000000001</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.3227</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.36244</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.28431</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.30341</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.31015</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.29689</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.32629</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.32931</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.33055</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.32667</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.33956</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.32497</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33021</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.35442</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.36598</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.33815</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.3357</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.33516</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.33004</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.33043</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.33064</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.33362</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.32878</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.34141</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.3354</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.33431</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.32754</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.34426</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.08721</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.32614</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.32624</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.31962</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.33072</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.32748</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.32817</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.32998</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.3339</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.34168</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>-0.02141</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>-0.02813</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>-0.01758</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>-0.03255</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.30227</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.24546</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.35681</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.27037</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.35869</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0.29361</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0.28878</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.28064</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.29998</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.26274</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.30942</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.30663</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.28377</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.28722</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.10092</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.21746</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.26948</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.30322</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.31096</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.14956</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.3178</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.31454</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.13953</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.04792</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.30839</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.28955</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.3099</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.31612</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.31894</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.32604</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.33581</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.32317</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.34652</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.3276</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.31664</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.31459</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.31639</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.31585</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.31577</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.3168</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.31239</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.31195</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.31479</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.31133</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.31369</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.37107</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.31351</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>-0.02771</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.31076</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.31504</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.30581</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.30336</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.31125</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.31672</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.31571</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.36795</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.35129</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.31382</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.33154</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.32528</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.33055</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.33078</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.3703</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.33085</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.33072</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.26357</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.31657</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.32008</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.32862</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.32914</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.33049</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.33158</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.33594</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.3451</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.28869</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.34919</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.34067</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.33594</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.32053</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.32035</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.33046</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.34654</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.33109</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.34022</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.35396</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.32319</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.36923</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.35529</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.36961</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.35945</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.31731</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>-0.01674</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.32974</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.32142</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.29942</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.43528</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.29827</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.52511</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.05619</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.26038</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.26825</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.3112</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.24527</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.21385</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.24048</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.22784</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.20866</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.21022</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.30479</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.36076</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.27148</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.20951</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.24008</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.2465</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.343</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.36323</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.32491</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.17771</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.23257</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.27629</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.26018</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.25844</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.23248</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.25463</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.30641</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.37517</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.35718</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.42504</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>0.43737</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.41685</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.43682</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.34348</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.34025</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.36712</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.40326</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.2814</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.35176</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.30872</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.4284</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.39423</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.34495</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.37769</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.42475</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.7043700000000001</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.42137</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.40265</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.45863</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.40039</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.38007</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.3624</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.34449</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.3253</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.3727200000000001</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.36422</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.36875</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.34704</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.44506</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.40099</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.40103</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.39162</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.38077</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.36016</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.3756</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.37448</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.37867</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.37738</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.36921</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.36695</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.36157</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.36004</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.35981</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.36041</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.3559</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.32893</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.35619</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.35112</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.34992</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.34724</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.35017</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.36021</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.37109</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.39971</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.37584</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.3696</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.31903</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.28123</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.08463</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.27653</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.02017</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>-0.03709</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.01595</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.02612</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>-0.0284</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.3221</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.2843</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.09487999999999999</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.30405</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.17339</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.31106</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.29414</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.29448</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.29335</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.26244</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.28037</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.27278</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.15672</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.31969</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.3384</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.30977</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.15259</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.18786</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.01476</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.0716</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.30117</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.26904</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.27237</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.31471</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.29248</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.31878</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.30068</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.33305</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.39795</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.3221</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.37383</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.35586</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.36028</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.43495</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.5311900000000001</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>0.52644</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0.34968</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.46068</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>0.5509500000000001</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.43293</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.30726</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.44654</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.35357</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0.49982</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.48102</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>0.71094</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0.75101</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.51975</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.52163</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.39838</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.44138</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.37224</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.37934</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.36961</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.37524</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.27135</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.36987</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.31955</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.37069</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.33478</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.33773</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.35014</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.32112</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.33475</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.34166</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.33859</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.33927</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.34581</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.33565</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.33772</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.33627</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.31359</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.32689</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.31947</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.31003</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.30548</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.30946</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.30983</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.29323</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.29301</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.34544</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.36334</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.30555</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.29193</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.2872</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.28134</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.27533</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.3154</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.26146</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.26281</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.27775</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.20858</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.23443</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.13771</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>-0.00949</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>-0.02191</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.24405</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.02337</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.03567</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.0286</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.01311</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>-0.00013</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.12452</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.11504</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.2106</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.18833</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.11251</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.329</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.24323</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.23803</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.3014</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.34376</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.22374</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.32521</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.33586</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.34652</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.29343</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.3757200000000001</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.39509</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.30507</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.37638</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.29713</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.39481</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.37605</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.37671</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.40218</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.38139</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.3625</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.27588</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.3238</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.38762</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.3566</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.35693</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.3735</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.38099</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.37613</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.35095</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0.7689900000000001</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.34263</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.40605</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.37911</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.34123</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.33759</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.35654</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.35597</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.38227</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.3459</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.34783</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.34236</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.37976</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.35464</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.36055</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.37941</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.37994</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.34882</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.35969</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.36329</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.3609</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.36424</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.35594</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.36592</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.35108</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.35126</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.34006</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.32264</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.32436</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.30271</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.30475</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.29709</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.26968</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.24177</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.22015</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.21099</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.18027</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.17946</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.18537</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.2378</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.06839000000000001</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>-0.01281</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>-0.02263</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>-0.02164</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.01551</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.08835</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.01567</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>-0.02957</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.01805</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>-0.03235</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>-0.04055</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>-0.02491</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.03664</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>-0.03944</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>-0.02311</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.13409</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>-0.0141</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.14733</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.16704</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.20898</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.35457</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>-0.02161</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.005059999999999999</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.00082</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.07020999999999999</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.34138</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.35707</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.45788</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.47464</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.33076</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.4326</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.35738</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.5341399999999999</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.38654</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.36378</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.46452</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.3995</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.39665</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.39782</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.41642</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.32726</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.36286</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.4424</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.35249</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.3982</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.40132</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.38858</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.37724</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.37114</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.39043</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.32993</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.50118</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.40142</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.4045899999999999</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.31946</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.37348</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.36271</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.36917</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.35022</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.41956</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.34828</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.37886</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.37323</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.34456</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.3432</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.34996</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.33335</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.3174</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.35023</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.32336</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.32075</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.33304</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.36451</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.34044</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.35555</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.34173</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.34971</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.34221</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.32478</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.29495</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.25836</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.22307</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.20366</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.13497</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.1821</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.22119</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.2087</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.12968</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.14041</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.02151</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.11193</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>-0.03493</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>-0.03756</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>-0.03876</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>-0.04079</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>-0.0319</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.01121</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>-0.044</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.03535</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>-0.0252</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>-0.0344</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>-0.04308</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0.08234999999999999</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>-0.04174</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>-0.04543</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>-0.0422</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>-0.03395</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>-0.04076</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>-0.04399</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>-0.03387</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>-0.0254</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>-0.03801</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>-0.03773</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>-0.02915</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>-0.02783</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.18326</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.21641</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.23756</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.24207</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.24863</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.26416</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.27018</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.27185</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.30387</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.36612</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.39861</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.33092</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.3185</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.2899</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.35373</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.36195</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.37923</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.35748</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.35308</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.38406</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.40909</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.38968</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.48117</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.3887</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.41907</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.43457</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.41352</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.39494</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.40872</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.40984</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.38401</v>
       </c>
     </row>
   </sheetData>
